--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251205_201603.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251205_201603.xlsx
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5226,7 +5226,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5444,7 +5444,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5584,7 +5584,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5876,7 +5876,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251205_201603.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251205_201603.xlsx
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5226,7 +5226,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5444,7 +5444,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5584,7 +5584,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5876,7 +5876,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7818,7 +7818,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251205_201603.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251205_201603.xlsx
@@ -5584,7 +5584,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5876,7 +5876,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7818,7 +7818,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251205_201603.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251205_201603.xlsx
@@ -7666,7 +7666,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7818,7 +7818,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251205_201603.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251205_201603.xlsx
@@ -7666,7 +7666,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7818,7 +7818,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251205_201603.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251205_201603.xlsx
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5226,7 +5226,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5444,7 +5444,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251205_201603.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251205_201603.xlsx
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5226,7 +5226,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5444,7 +5444,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5584,7 +5584,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5876,7 +5876,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251205_201603.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251205_201603.xlsx
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5226,7 +5226,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5444,7 +5444,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251205_201603.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251205_201603.xlsx
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5226,7 +5226,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5444,7 +5444,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5584,7 +5584,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5876,7 +5876,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7818,7 +7818,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251205_201603.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251205_201603.xlsx
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5226,7 +5226,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5444,7 +5444,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7818,7 +7818,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251205_201603.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251205_201603.xlsx
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5226,7 +5226,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5444,7 +5444,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5584,7 +5584,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5876,7 +5876,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7818,7 +7818,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251205_201603.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251205_201603.xlsx
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5226,7 +5226,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5444,7 +5444,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7818,7 +7818,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
